--- a/.pic/Labs/lab_03_memory/fig_03.xlsx
+++ b/.pic/Labs/lab_03_memory/fig_03.xlsx
@@ -55,10 +55,14 @@
     <t>byte enable bit indices</t>
   </si>
   <si>
-    <t>MSB (Most Significant Byte) — the byte containing the most significant bits of a number</t>
-  </si>
-  <si>
-    <t>LSB (Least Significant Byte) — the byte containing the least significant bits of a number</t>
+    <t>MSB — most significant byte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSB — least significant byte
+LSB — least significant byte
+LSB — least significant byte
+LSB — least significant byte
+</t>
   </si>
 </sst>
 </file>
@@ -283,20 +287,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -339,6 +331,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,151 +549,151 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="3:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="6">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="17"/>
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="D8" s="11">
+      <c r="D8" s="7">
         <v>7</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="8">
         <v>6</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="9">
         <v>4</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="10">
         <v>1</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="8">
         <v>9</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="9">
         <v>8</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="10">
         <v>2</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
     </row>
     <row r="10" spans="3:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="14">
         <v>3</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="D11" s="19">
+      <c r="D11" s="15">
         <v>3</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="15">
         <v>2</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="15">
         <v>1</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
     </row>
     <row r="15" spans="3:11" x14ac:dyDescent="0.3">
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
